--- a/02_DIA_inicio_2026_analisis_assets/ranking_establecimientos_logro.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/ranking_establecimientos_logro.xlsx
@@ -404,7 +404,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Escuela Basica Pablo Neruda</t>
+          <t>Escuela Básica Pablo Neruda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Escuela Basica Educadores De Chile</t>
+          <t>Escuela Básica Educadores De Chile</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Escuela Raul Saez Saez</t>
+          <t>Escuela Raul Saéz Saéz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Escuela Basica Sendero Del Saber</t>
+          <t>Escuela Básica Sendero Del Saber</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Esc. Basica Municipal Risopatron</t>
+          <t>Esc. Básica Municipal Risopatrón</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Escuela Basica República De Las Filipinas</t>
+          <t>Escuela Básica República De Las Filipinas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Escuela Basica Salomon Sack</t>
+          <t>Escuela Básica Salomón Sack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1063,13 +1063,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96FAD6C-EC24-4D31-9588-082077C48BDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F81E1D2-3D43-44EF-AF89-7FE6CF852733}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40066673-4331-4824-9570-92BE5DFA5D2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24541134-165E-438E-B277-07746CC7E784}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E67F06-CE8D-4ED6-94A0-808F4AB9D5F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B10AF96-407F-4E18-BC0C-D57926892C98}"/>
 </file>